--- a/static/ejemplo_dc3.xlsx
+++ b/static/ejemplo_dc3.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DC3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Plantilla DC-3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Plantilla DC-3'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +27,60 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A4786"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A4786"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +88,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="0094A3B8"/>
+      </left>
+      <right style="thin">
+        <color rgb="0094A3B8"/>
+      </right>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0094A3B8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -122,6 +203,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="314325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,417 +524,301 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="31" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Plantilla DC-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>💡 Si no ves todo el texto, haz más grande la celda para ver todas las instrucciones completas.
+INSTRUCCIONES:
+• Complete los datos de los participantes.
+• El campo NOMBRE debe ir como: Apellido Paterno + Apellido Materno + Nombre(s)   Ej: López Hernández María Fernanda
+• La fila de ejemplo debe borrarse antes de procesar.
+• La columna FOLIO es opcional — si la deja vacía, el sistema asigna una automáticamente.
+Para DC-3:
+• CURP debe tener exactamente 18 caracteres.
+• El RFC es el de la EMPRESA (no del participante). Persona Moral: 12 caracteres · Persona Física: 13 caracteres.
+• En EMPRESA escriba la Razón Social completa.
+• En ÁREA TEMÁTICA escriba: CÓDIGO + NOMBRE   Ej: 6000 Seguridad
+• REPRESENTANTE LEGAL puede quedar vacío — si lo deja vacío, se usa el valor por defecto configurado en el sistema.
+─── ¿QUIÉN LLENA CADA CAMPO? ───
+🟡  AMARILLO  →  Los llena el CLIENTE (usted):
+       Nombre, CURP, Puesto, Empresa, RFC, Representante Legal
+⬜  BLANCO    →  Los llena AGASI:
+       Curso, Duracion, Fechas, Area Tematica, Ocupacion, Instructor, Folio</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1"/>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>CURP</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Puesto</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Empresa (Razón Social)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>RFC (de la Empresa)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Representante Legal</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Curso</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Duracion (hrs)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Fecha Inicio</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Fecha Fin</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Area Tematica</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Ocupacion</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Puesto</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>RFC</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Curso</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Duracion (hrs)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Fecha Inicio</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Fecha Fin</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Area Tematica</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Instructor</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Folio</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>López Hernández María Fernanda</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>LOHF900215HGPLRR09</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>09.4 Protección de bienes y/o personas</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Supervisor de Seguridad</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Industrias Peoles SAB de CV</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Industrias Peoles</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>IPE850101AB1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Ing. Alejandro García Salinas</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Seguridad Industrial y Protección Civil</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>6000 Seguridad</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Ing. Roberto Martínez Cruz</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>DC3-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Mendoza Ruiz Carlos Alberto</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MERA880507HHCPRR02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>04.6 Procesos industriales</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Operador</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Industrias Peoles SAB de CV</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>IPE850101AB1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Manejo de Materiales Peligrosos</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>24</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>6000 Seguridad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Ing. Roberto Martínez Cruz</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>DC3-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Pérez García Juan</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PEGJ910320HMCNRR05</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>04.2 Electricidad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Técnico de Mantenimiento</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CEMEX México SAB de CV</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CMX010101AB2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Primeros Auxilios y RCP</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>6000 Seguridad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Dra. Ana Ruiz López</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>DC3-003</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ramírez Cruz Ana Sofía</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>RACZ940812MMPRR08</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>09.2 Inspección sanitaria y del medio ambiente</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Encargada Ambiental</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CEMEX México SAB de CV</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CMX010101AB2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ISO 14001:2015 Sistemas de Gestión Ambiental</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>32</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>3000 Administración, contabilidad y economía</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Ing. Alejandro García Salinas</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>DC3-004</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>González Silva Roberto</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>GOSR870904HHCPRR03</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>09.4 Protección de bienes y/o personas</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Jefe de Seguridad</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Intermex Manufactura SA de CV</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>IMA020202AB3</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Evaluación de Riesgos y Peligros en el Trabajo</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>20</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>6000 Seguridad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Ing. Roberto Martínez Cruz</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>DC3-005</t>
-        </is>
-      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>09.4 Protección</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Ing. Roberto Martínez</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr"/>
+      <c r="B9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+      <c r="N10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr"/>
+      <c r="B11" s="6" t="inlineStr"/>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr"/>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" s="7" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+      <c r="N12" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N4"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>